--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/134.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/134.xlsx
@@ -426,13 +426,13 @@
         <v>-19.01358041959463</v>
       </c>
       <c r="E2">
-        <v>-13.41965025171988</v>
+        <v>-16.9088394746299</v>
       </c>
       <c r="F2">
-        <v>-1.142062451094967</v>
+        <v>-1.038265573544108</v>
       </c>
       <c r="G2">
-        <v>-11.53955318417821</v>
+        <v>-13.53224999735848</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.5060231304202</v>
       </c>
       <c r="E3">
-        <v>-13.54570938267141</v>
+        <v>-15.3805700665213</v>
       </c>
       <c r="F3">
-        <v>-0.656168014737863</v>
+        <v>-1.479869298417074</v>
       </c>
       <c r="G3">
-        <v>-11.2347082192855</v>
+        <v>-13.38368926628369</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.93679432354224</v>
       </c>
       <c r="E4">
-        <v>-14.56409978836036</v>
+        <v>-17.54666145318824</v>
       </c>
       <c r="F4">
-        <v>-0.792921812389017</v>
+        <v>-0.6724136700184409</v>
       </c>
       <c r="G4">
-        <v>-10.15260013050055</v>
+        <v>-13.56126196319189</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.3617624004068</v>
       </c>
       <c r="E5">
-        <v>-14.40600623227858</v>
+        <v>-18.15996627346906</v>
       </c>
       <c r="F5">
-        <v>-0.7866590473464117</v>
+        <v>-1.928621079939376</v>
       </c>
       <c r="G5">
-        <v>-10.26362920679663</v>
+        <v>-12.45755422003596</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.7542676475724</v>
       </c>
       <c r="E6">
-        <v>-14.65410320926281</v>
+        <v>-18.03696386247272</v>
       </c>
       <c r="F6">
-        <v>-0.4098344373856228</v>
+        <v>-1.615067105006309</v>
       </c>
       <c r="G6">
-        <v>-10.03237435869638</v>
+        <v>-11.89088151898783</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.12576659030991</v>
       </c>
       <c r="E7">
-        <v>-16.53176702943321</v>
+        <v>-19.70043991902833</v>
       </c>
       <c r="F7">
-        <v>-0.2880205294877667</v>
+        <v>-1.170747324488364</v>
       </c>
       <c r="G7">
-        <v>-10.0407136229098</v>
+        <v>-11.26935638889952</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.4655415134913</v>
       </c>
       <c r="E8">
-        <v>-16.59538756076697</v>
+        <v>-19.93806706410682</v>
       </c>
       <c r="F8">
-        <v>-0.7048234197249514</v>
+        <v>-2.221912329537354</v>
       </c>
       <c r="G8">
-        <v>-9.194061464514432</v>
+        <v>-11.13024064424826</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.7771273924679</v>
       </c>
       <c r="E9">
-        <v>-17.87875709454075</v>
+        <v>-21.53118874847926</v>
       </c>
       <c r="F9">
-        <v>-0.8092870374662106</v>
+        <v>-0.8601738840881531</v>
       </c>
       <c r="G9">
-        <v>-8.045017455470953</v>
+        <v>-10.86820765426941</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.06807301065414</v>
       </c>
       <c r="E10">
-        <v>-17.4282645002577</v>
+        <v>-19.61987383795786</v>
       </c>
       <c r="F10">
-        <v>-0.3982876375561537</v>
+        <v>-0.9070151539491057</v>
       </c>
       <c r="G10">
-        <v>-8.500750464952564</v>
+        <v>-9.001791600684639</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.34737704972133</v>
       </c>
       <c r="E11">
-        <v>-17.43029778508715</v>
+        <v>-21.03988554643909</v>
       </c>
       <c r="F11">
-        <v>-0.3947258829523304</v>
+        <v>-0.50891266316143</v>
       </c>
       <c r="G11">
-        <v>-7.681920131269228</v>
+        <v>-9.73824894025983</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.64424607614859</v>
       </c>
       <c r="E12">
-        <v>-17.86210589561454</v>
+        <v>-20.95920172504443</v>
       </c>
       <c r="F12">
-        <v>-0.3421658510307261</v>
+        <v>-0.9103757779016681</v>
       </c>
       <c r="G12">
-        <v>-6.891434688493132</v>
+        <v>-9.724480381362001</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.97658794737556</v>
       </c>
       <c r="E13">
-        <v>-18.32449479111574</v>
+        <v>-20.88221766691403</v>
       </c>
       <c r="F13">
-        <v>-0.3127984003877746</v>
+        <v>-1.600952326034955</v>
       </c>
       <c r="G13">
-        <v>-6.544711322528643</v>
+        <v>-8.277709080335246</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.38886781967448</v>
       </c>
       <c r="E14">
-        <v>-18.30241395185434</v>
+        <v>-22.21100779498474</v>
       </c>
       <c r="F14">
-        <v>-0.08749089462186621</v>
+        <v>-0.2521282104732048</v>
       </c>
       <c r="G14">
-        <v>-6.477533732445752</v>
+        <v>-9.143416738854661</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.90744944538873</v>
       </c>
       <c r="E15">
-        <v>-20.68570453735117</v>
+        <v>-24.44319225979363</v>
       </c>
       <c r="F15">
-        <v>-0.6013907945346434</v>
+        <v>-0.1959866276238341</v>
       </c>
       <c r="G15">
-        <v>-5.333256908978823</v>
+        <v>-8.80338398542504</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.5568360149777</v>
       </c>
       <c r="E16">
-        <v>-20.60822234707993</v>
+        <v>-24.50616521934429</v>
       </c>
       <c r="F16">
-        <v>0.04360590549933809</v>
+        <v>-0.2673531672912819</v>
       </c>
       <c r="G16">
-        <v>-5.612097538660557</v>
+        <v>-6.876272389923271</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.34892786013225</v>
       </c>
       <c r="E17">
-        <v>-20.94610537821424</v>
+        <v>-25.03448869639717</v>
       </c>
       <c r="F17">
-        <v>0.4466551017138889</v>
+        <v>-0.008566910325941342</v>
       </c>
       <c r="G17">
-        <v>-5.700406340920616</v>
+        <v>-5.78138228481119</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.27329930830423</v>
       </c>
       <c r="E18">
-        <v>-23.75959193749174</v>
+        <v>-27.15561233616794</v>
       </c>
       <c r="F18">
-        <v>0.7046130804854547</v>
+        <v>0.3811831154637066</v>
       </c>
       <c r="G18">
-        <v>-5.395567997118985</v>
+        <v>-7.349832687133857</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.31434315470626</v>
       </c>
       <c r="E19">
-        <v>-24.76395765917895</v>
+        <v>-26.79121056124472</v>
       </c>
       <c r="F19">
-        <v>1.075445739115178</v>
+        <v>0.7218010407857189</v>
       </c>
       <c r="G19">
-        <v>-4.555960679631184</v>
+        <v>-5.610028447698513</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.43278964602367</v>
       </c>
       <c r="E20">
-        <v>-23.43531244227648</v>
+        <v>-27.08910263841729</v>
       </c>
       <c r="F20">
-        <v>1.059135151892068</v>
+        <v>0.9600949350582308</v>
       </c>
       <c r="G20">
-        <v>-5.555887785949271</v>
+        <v>-6.821380234336615</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.59697266379089</v>
       </c>
       <c r="E21">
-        <v>-24.49813170645469</v>
+        <v>-26.70834854385237</v>
       </c>
       <c r="F21">
-        <v>1.352439071137369</v>
+        <v>1.178035040905515</v>
       </c>
       <c r="G21">
-        <v>-5.249940409391986</v>
+        <v>-7.093460730027156</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.76132754775725</v>
       </c>
       <c r="E22">
-        <v>-25.42323101911163</v>
+        <v>-30.61783676059928</v>
       </c>
       <c r="F22">
-        <v>1.676553988967544</v>
+        <v>1.396480348939824</v>
       </c>
       <c r="G22">
-        <v>-4.815418065180485</v>
+        <v>-5.995829493208559</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.8917837287793</v>
       </c>
       <c r="E23">
-        <v>-25.19004177856065</v>
+        <v>-27.75431282777403</v>
       </c>
       <c r="F23">
-        <v>1.608834724023354</v>
+        <v>1.149415891307609</v>
       </c>
       <c r="G23">
-        <v>-4.855614709118316</v>
+        <v>-5.874100733729557</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.95956506225381</v>
       </c>
       <c r="E24">
-        <v>-26.20556113172874</v>
+        <v>-28.5155991216775</v>
       </c>
       <c r="F24">
-        <v>1.843549442926972</v>
+        <v>1.474165875209875</v>
       </c>
       <c r="G24">
-        <v>-5.809455710984209</v>
+        <v>-5.697218285566298</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.94281677427498</v>
       </c>
       <c r="E25">
-        <v>-25.80747656713646</v>
+        <v>-30.24762268928721</v>
       </c>
       <c r="F25">
-        <v>1.94758308451219</v>
+        <v>1.013307453816996</v>
       </c>
       <c r="G25">
-        <v>-5.860173268645844</v>
+        <v>-5.228458279387655</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.83565919297124</v>
       </c>
       <c r="E26">
-        <v>-26.11210248515844</v>
+        <v>-28.74623883136216</v>
       </c>
       <c r="F26">
-        <v>2.284584617376296</v>
+        <v>1.757908961843669</v>
       </c>
       <c r="G26">
-        <v>-5.487515088926703</v>
+        <v>-6.797776044641611</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.63476261485195</v>
       </c>
       <c r="E27">
-        <v>-26.2636297539291</v>
+        <v>-29.06972584362608</v>
       </c>
       <c r="F27">
-        <v>1.941010704963116</v>
+        <v>1.15259280537398</v>
       </c>
       <c r="G27">
-        <v>-4.862199384195926</v>
+        <v>-5.590754451568876</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.35727587362585</v>
       </c>
       <c r="E28">
-        <v>-26.25314180812734</v>
+        <v>-30.24008957277545</v>
       </c>
       <c r="F28">
-        <v>2.411797378739885</v>
+        <v>1.787665212288861</v>
       </c>
       <c r="G28">
-        <v>-5.741817955071359</v>
+        <v>-5.827921934002264</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.02168981003635</v>
       </c>
       <c r="E29">
-        <v>-25.75780826422033</v>
+        <v>-28.93959108606766</v>
       </c>
       <c r="F29">
-        <v>1.864794857782592</v>
+        <v>1.555194604667419</v>
       </c>
       <c r="G29">
-        <v>-5.543784431457696</v>
+        <v>-5.877146435625687</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.661769327911566</v>
       </c>
       <c r="E30">
-        <v>-26.34398752519521</v>
+        <v>-30.16603996580202</v>
       </c>
       <c r="F30">
-        <v>2.199001149705948</v>
+        <v>1.664685696837241</v>
       </c>
       <c r="G30">
-        <v>-5.834172243980408</v>
+        <v>-4.975860344195724</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.30998046616752</v>
       </c>
       <c r="E31">
-        <v>-26.58767829696997</v>
+        <v>-29.08143194893591</v>
       </c>
       <c r="F31">
-        <v>2.644071606827811</v>
+        <v>2.062167374906064</v>
       </c>
       <c r="G31">
-        <v>-5.267201593833746</v>
+        <v>-6.795932070776237</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.994180225679905</v>
       </c>
       <c r="E32">
-        <v>-25.20536613460261</v>
+        <v>-30.21265154876297</v>
       </c>
       <c r="F32">
-        <v>2.089689016304571</v>
+        <v>1.171579855594184</v>
       </c>
       <c r="G32">
-        <v>-4.980481865768547</v>
+        <v>-7.406399978763384</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.742345552851772</v>
       </c>
       <c r="E33">
-        <v>-24.94719783142532</v>
+        <v>-30.48388676368939</v>
       </c>
       <c r="F33">
-        <v>1.481131013825978</v>
+        <v>1.502454030271455</v>
       </c>
       <c r="G33">
-        <v>-5.081132381799009</v>
+        <v>-6.023416269187305</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.564997359755113</v>
       </c>
       <c r="E34">
-        <v>-24.38373339607292</v>
+        <v>-28.34955809371226</v>
       </c>
       <c r="F34">
-        <v>1.813425772709399</v>
+        <v>1.3657770423572</v>
       </c>
       <c r="G34">
-        <v>-5.893702473867582</v>
+        <v>-6.04788120072252</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.470404496211913</v>
       </c>
       <c r="E35">
-        <v>-24.6861177194611</v>
+        <v>-26.71217057591484</v>
       </c>
       <c r="F35">
-        <v>1.816219429944234</v>
+        <v>0.9746396901856268</v>
       </c>
       <c r="G35">
-        <v>-4.692802079496959</v>
+        <v>-5.163667592638578</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.447698631580565</v>
       </c>
       <c r="E36">
-        <v>-24.71258212156192</v>
+        <v>-27.0220404668377</v>
       </c>
       <c r="F36">
-        <v>1.790045522279766</v>
+        <v>1.541622244972103</v>
       </c>
       <c r="G36">
-        <v>-4.912301180387256</v>
+        <v>-5.894318235337886</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.489669964585758</v>
       </c>
       <c r="E37">
-        <v>-23.67509061250862</v>
+        <v>-29.58646548416734</v>
       </c>
       <c r="F37">
-        <v>1.696611624386585</v>
+        <v>1.149392135718877</v>
       </c>
       <c r="G37">
-        <v>-4.543662002952792</v>
+        <v>-6.357993243568209</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.57731405902811</v>
       </c>
       <c r="E38">
-        <v>-22.64244457064351</v>
+        <v>-28.75791776582794</v>
       </c>
       <c r="F38">
-        <v>1.790519050348482</v>
+        <v>1.622714322666265</v>
       </c>
       <c r="G38">
-        <v>-4.946194545618315</v>
+        <v>-5.974731386486783</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.690441548289526</v>
       </c>
       <c r="E39">
-        <v>-23.73249807750385</v>
+        <v>-25.9106986036673</v>
       </c>
       <c r="F39">
-        <v>2.187451182464648</v>
+        <v>2.150728209697438</v>
       </c>
       <c r="G39">
-        <v>-5.223843378905911</v>
+        <v>-6.099201277672302</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.81533582128405</v>
       </c>
       <c r="E40">
-        <v>-23.09342171164538</v>
+        <v>-27.26778716581195</v>
       </c>
       <c r="F40">
-        <v>1.929893089436731</v>
+        <v>1.304053688008863</v>
       </c>
       <c r="G40">
-        <v>-5.228362273567016</v>
+        <v>-6.042806134410817</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.936210532863026</v>
       </c>
       <c r="E41">
-        <v>-22.01461693422009</v>
+        <v>-26.44304336563899</v>
       </c>
       <c r="F41">
-        <v>1.922132930451078</v>
+        <v>0.8101211522779461</v>
       </c>
       <c r="G41">
-        <v>-5.127771347356261</v>
+        <v>-6.035718256411237</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.051007202429529</v>
       </c>
       <c r="E42">
-        <v>-22.10354257830872</v>
+        <v>-26.0835051718</v>
       </c>
       <c r="F42">
-        <v>2.035567450350344</v>
+        <v>1.2831218469245</v>
       </c>
       <c r="G42">
-        <v>-4.678053599119506</v>
+        <v>-5.054075293106545</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.15449521937949</v>
       </c>
       <c r="E43">
-        <v>-21.97336706448423</v>
+        <v>-25.07949719955941</v>
       </c>
       <c r="F43">
-        <v>1.623984454810447</v>
+        <v>1.397744146260345</v>
       </c>
       <c r="G43">
-        <v>-5.612564325581594</v>
+        <v>-4.50619324853932</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.251236864173412</v>
       </c>
       <c r="E44">
-        <v>-19.32799557426748</v>
+        <v>-24.9659592992391</v>
       </c>
       <c r="F44">
-        <v>1.997061224722349</v>
+        <v>1.456943073379471</v>
       </c>
       <c r="G44">
-        <v>-4.246563714621978</v>
+        <v>-4.607734301319846</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.344213870950233</v>
       </c>
       <c r="E45">
-        <v>-21.090604455325</v>
+        <v>-23.57924093166226</v>
       </c>
       <c r="F45">
-        <v>2.045275567611987</v>
+        <v>2.031901171156101</v>
       </c>
       <c r="G45">
-        <v>-4.368676497383535</v>
+        <v>-6.167497832147466</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.439335101686</v>
       </c>
       <c r="E46">
-        <v>-19.54615028111299</v>
+        <v>-21.96718116898975</v>
       </c>
       <c r="F46">
-        <v>2.126207691008689</v>
+        <v>1.312257284650839</v>
       </c>
       <c r="G46">
-        <v>-4.170844917047767</v>
+        <v>-5.633281719566353</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.549498540448406</v>
       </c>
       <c r="E47">
-        <v>-20.34370512334389</v>
+        <v>-24.37241221105374</v>
       </c>
       <c r="F47">
-        <v>2.425385575494355</v>
+        <v>0.6253929431833426</v>
       </c>
       <c r="G47">
-        <v>-4.926837785850196</v>
+        <v>-6.621290861943065</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.678597107006905</v>
       </c>
       <c r="E48">
-        <v>-18.83020759744832</v>
+        <v>-21.71432476582346</v>
       </c>
       <c r="F48">
-        <v>1.898123948773015</v>
+        <v>1.464251876179224</v>
       </c>
       <c r="G48">
-        <v>-4.425538427566057</v>
+        <v>-5.325324841866729</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.840704161946327</v>
       </c>
       <c r="E49">
-        <v>-19.11406140519712</v>
+        <v>-22.83878561819408</v>
       </c>
       <c r="F49">
-        <v>1.865388747500882</v>
+        <v>1.799468572476631</v>
       </c>
       <c r="G49">
-        <v>-4.230583711303916</v>
+        <v>-5.906785749838781</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.03576337073955</v>
       </c>
       <c r="E50">
-        <v>-18.21486043539004</v>
+        <v>-23.25335835664828</v>
       </c>
       <c r="F50">
-        <v>1.597644258024858</v>
+        <v>1.351873688125557</v>
       </c>
       <c r="G50">
-        <v>-5.051853917049694</v>
+        <v>-4.247520462282827</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.26786989695166</v>
       </c>
       <c r="E51">
-        <v>-18.67483112577114</v>
+        <v>-21.67778450905556</v>
       </c>
       <c r="F51">
-        <v>1.394136464184974</v>
+        <v>1.442135423070113</v>
       </c>
       <c r="G51">
-        <v>-4.704283051427152</v>
+        <v>-5.995322979741051</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.53109922638776</v>
       </c>
       <c r="E52">
-        <v>-18.24485704721685</v>
+        <v>-22.56407027099276</v>
       </c>
       <c r="F52">
-        <v>1.15808668119464</v>
+        <v>1.351214866464734</v>
       </c>
       <c r="G52">
-        <v>-4.894228912288375</v>
+        <v>-5.136607193400576</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.81984216453815</v>
       </c>
       <c r="E53">
-        <v>-17.07687303115851</v>
+        <v>-22.04961750982538</v>
       </c>
       <c r="F53">
-        <v>1.86136455076975</v>
+        <v>1.53143109740625</v>
       </c>
       <c r="G53">
-        <v>-4.022770836167245</v>
+        <v>-4.362896284871967</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.12907600106894</v>
       </c>
       <c r="E54">
-        <v>-17.37887696273005</v>
+        <v>-21.6145126702204</v>
       </c>
       <c r="F54">
-        <v>1.572024647430794</v>
+        <v>1.327253395964135</v>
       </c>
       <c r="G54">
-        <v>-3.796514911831296</v>
+        <v>-4.430255954959518</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.44400865071316</v>
       </c>
       <c r="E55">
-        <v>-16.30869892828937</v>
+        <v>-19.32241196581602</v>
       </c>
       <c r="F55">
-        <v>1.895748389899856</v>
+        <v>1.057787418158029</v>
       </c>
       <c r="G55">
-        <v>-4.183997714475292</v>
+        <v>-4.914515935353029</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.76537023302719</v>
       </c>
       <c r="E56">
-        <v>-16.62888921147572</v>
+        <v>-20.11366770070225</v>
       </c>
       <c r="F56">
-        <v>1.425351307778285</v>
+        <v>1.380328132308257</v>
       </c>
       <c r="G56">
-        <v>-3.136464963302485</v>
+        <v>-5.752100509516335</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.08039327337495</v>
       </c>
       <c r="E57">
-        <v>-17.09208870382428</v>
+        <v>-19.1138168676007</v>
       </c>
       <c r="F57">
-        <v>1.453509598954799</v>
+        <v>0.869872792761561</v>
       </c>
       <c r="G57">
-        <v>-4.764448906057866</v>
+        <v>-6.241551425315423</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.38620584187263</v>
       </c>
       <c r="E58">
-        <v>-15.88451676799089</v>
+        <v>-20.74866391147981</v>
       </c>
       <c r="F58">
-        <v>1.918602849965563</v>
+        <v>1.723388924004835</v>
       </c>
       <c r="G58">
-        <v>-5.163952299554956</v>
+        <v>-7.185785224026351</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.67082556566638</v>
       </c>
       <c r="E59">
-        <v>-16.28092126872632</v>
+        <v>-19.85656811739078</v>
       </c>
       <c r="F59">
-        <v>1.890286188197506</v>
+        <v>0.7239232067124078</v>
       </c>
       <c r="G59">
-        <v>-3.932296937124503</v>
+        <v>-5.160423258010093</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.92878173093424</v>
       </c>
       <c r="E60">
-        <v>-16.69464265406709</v>
+        <v>-17.57923929519942</v>
       </c>
       <c r="F60">
-        <v>1.617956870096285</v>
+        <v>1.076106144481917</v>
       </c>
       <c r="G60">
-        <v>-4.845252701580397</v>
+        <v>-5.846265666835365</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.15429212957754</v>
       </c>
       <c r="E61">
-        <v>-16.1339632302294</v>
+        <v>-17.80850687725976</v>
       </c>
       <c r="F61">
-        <v>1.63235592427946</v>
+        <v>1.200433393667575</v>
       </c>
       <c r="G61">
-        <v>-4.330198026580586</v>
+        <v>-5.352219713827769</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.34055646810863</v>
       </c>
       <c r="E62">
-        <v>-16.59692271345557</v>
+        <v>-19.53292260853658</v>
       </c>
       <c r="F62">
-        <v>1.973272378166533</v>
+        <v>1.404706117464617</v>
       </c>
       <c r="G62">
-        <v>-4.92868507026111</v>
+        <v>-6.243425194090651</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.49087198581624</v>
       </c>
       <c r="E63">
-        <v>-15.09101943847086</v>
+        <v>-19.86465597196847</v>
       </c>
       <c r="F63">
-        <v>1.261160596995101</v>
+        <v>0.9106357993190569</v>
       </c>
       <c r="G63">
-        <v>-4.313489703243884</v>
+        <v>-6.981713265349057</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.59860549857101</v>
       </c>
       <c r="E64">
-        <v>-16.49466071341436</v>
+        <v>-17.86990845632976</v>
       </c>
       <c r="F64">
-        <v>1.589039983786276</v>
+        <v>1.465013638724551</v>
       </c>
       <c r="G64">
-        <v>-4.679920746803655</v>
+        <v>-6.874703191337656</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.6681765629172</v>
       </c>
       <c r="E65">
-        <v>-16.16933966917733</v>
+        <v>-18.97990083424587</v>
       </c>
       <c r="F65">
-        <v>1.503915790831406</v>
+        <v>1.142499847574885</v>
       </c>
       <c r="G65">
-        <v>-4.741659110565523</v>
+        <v>-6.457534726843015</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.69376969520212</v>
       </c>
       <c r="E66">
-        <v>-14.40045885161918</v>
+        <v>-17.51999326975707</v>
       </c>
       <c r="F66">
-        <v>1.839821399202028</v>
+        <v>0.9048647749631956</v>
       </c>
       <c r="G66">
-        <v>-4.232172773162766</v>
+        <v>-6.113466418401021</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.68026482092304</v>
       </c>
       <c r="E67">
-        <v>-15.96721576031897</v>
+        <v>-18.04739293811238</v>
       </c>
       <c r="F67">
-        <v>1.627729919300462</v>
+        <v>1.055571813582329</v>
       </c>
       <c r="G67">
-        <v>-4.430388376781089</v>
+        <v>-5.329214732875373</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.62568786517857</v>
       </c>
       <c r="E68">
-        <v>-16.18492667671173</v>
+        <v>-17.34101892002592</v>
       </c>
       <c r="F68">
-        <v>1.672694497651618</v>
+        <v>1.393051625632898</v>
       </c>
       <c r="G68">
-        <v>-4.169305513372006</v>
+        <v>-4.571271952750314</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.53624140009996</v>
       </c>
       <c r="E69">
-        <v>-15.45433437963225</v>
+        <v>-18.31567785222281</v>
       </c>
       <c r="F69">
-        <v>1.95036090468787</v>
+        <v>1.284323879714318</v>
       </c>
       <c r="G69">
-        <v>-4.1958593991425</v>
+        <v>-6.245904792699565</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.41832167589177</v>
       </c>
       <c r="E70">
-        <v>-14.42695042456406</v>
+        <v>-17.78099186918915</v>
       </c>
       <c r="F70">
-        <v>1.148593947937496</v>
+        <v>1.301956861376821</v>
       </c>
       <c r="G70">
-        <v>-4.763045234749215</v>
+        <v>-5.886518590047364</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.27344884339132</v>
       </c>
       <c r="E71">
-        <v>-16.16300886251461</v>
+        <v>-17.82551582563257</v>
       </c>
       <c r="F71">
-        <v>0.9898084254437058</v>
+        <v>1.09269704765206</v>
       </c>
       <c r="G71">
-        <v>-3.459322606474368</v>
+        <v>-5.386957268171342</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.11542822542352</v>
       </c>
       <c r="E72">
-        <v>-15.28710236300299</v>
+        <v>-16.40635999873879</v>
       </c>
       <c r="F72">
-        <v>1.58381217055941</v>
+        <v>0.6195965795328342</v>
       </c>
       <c r="G72">
-        <v>-4.710483703222207</v>
+        <v>-4.502641033175682</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.94866821515104</v>
       </c>
       <c r="E73">
-        <v>-14.54314653912687</v>
+        <v>-16.88885984730805</v>
       </c>
       <c r="F73">
-        <v>1.713948453042901</v>
+        <v>1.319238260326096</v>
       </c>
       <c r="G73">
-        <v>-3.81906965859035</v>
+        <v>-4.788115996118115</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.78946751361018</v>
       </c>
       <c r="E74">
-        <v>-14.50695950333158</v>
+        <v>-16.84043234627003</v>
       </c>
       <c r="F74">
-        <v>1.356989058232426</v>
+        <v>0.6695387455762172</v>
       </c>
       <c r="G74">
-        <v>-4.23619508599298</v>
+        <v>-6.015202805704374</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.64078077069628</v>
       </c>
       <c r="E75">
-        <v>-15.12471128508793</v>
+        <v>-18.08605704918988</v>
       </c>
       <c r="F75">
-        <v>1.324198427253253</v>
+        <v>1.120879094417305</v>
       </c>
       <c r="G75">
-        <v>-3.923199557982586</v>
+        <v>-5.095030051972869</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.51648848904338</v>
       </c>
       <c r="E76">
-        <v>-15.59502953857656</v>
+        <v>-19.06568371737317</v>
       </c>
       <c r="F76">
-        <v>1.00503100670291</v>
+        <v>0.4908911753439435</v>
       </c>
       <c r="G76">
-        <v>-3.042524923080125</v>
+        <v>-5.456644251773</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.42122232681273</v>
       </c>
       <c r="E77">
-        <v>-16.54025791819759</v>
+        <v>-17.51713580265823</v>
       </c>
       <c r="F77">
-        <v>1.467248247771236</v>
+        <v>0.6774826144480615</v>
       </c>
       <c r="G77">
-        <v>-3.304303001052455</v>
+        <v>-7.221072328929443</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.35651612395469</v>
       </c>
       <c r="E78">
-        <v>-17.22951430453506</v>
+        <v>-18.07156593236533</v>
       </c>
       <c r="F78">
-        <v>0.9717383409485417</v>
+        <v>0.378701448294213</v>
       </c>
       <c r="G78">
-        <v>-3.067598994994566</v>
+        <v>-4.825664203624529</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.32855713980773</v>
       </c>
       <c r="E79">
-        <v>-18.01011001160724</v>
+        <v>-20.32527423413267</v>
       </c>
       <c r="F79">
-        <v>1.073570631311298</v>
+        <v>0.7483914631059473</v>
       </c>
       <c r="G79">
-        <v>-3.656849616620523</v>
+        <v>-3.0622657061308</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.33058688280438</v>
       </c>
       <c r="E80">
-        <v>-16.94650279295169</v>
+        <v>-18.3585942003935</v>
       </c>
       <c r="F80">
-        <v>0.9965328407606617</v>
+        <v>0.2794157570434832</v>
       </c>
       <c r="G80">
-        <v>-2.939431224441682</v>
+        <v>-4.256114638502775</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.36390807606973</v>
       </c>
       <c r="E81">
-        <v>-18.96103521152992</v>
+        <v>-19.50738654360733</v>
       </c>
       <c r="F81">
-        <v>0.7197723135080411</v>
+        <v>0.5444687383162178</v>
       </c>
       <c r="G81">
-        <v>-2.58754009689039</v>
+        <v>-4.333942253585501</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.41660017113231</v>
       </c>
       <c r="E82">
-        <v>-18.1955329083253</v>
+        <v>-21.34473335968744</v>
       </c>
       <c r="F82">
-        <v>0.8104885720503281</v>
+        <v>0.1587207373748852</v>
       </c>
       <c r="G82">
-        <v>-2.168090666519191</v>
+        <v>-3.385709315863134</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.48731528840085</v>
       </c>
       <c r="E83">
-        <v>-18.52239816219895</v>
+        <v>-18.66280802728078</v>
       </c>
       <c r="F83">
-        <v>0.8947765682818463</v>
+        <v>0.5278382424981881</v>
       </c>
       <c r="G83">
-        <v>-1.930098858246525</v>
+        <v>-3.351100872795593</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.56700386964954</v>
       </c>
       <c r="E84">
-        <v>-20.02399938687637</v>
+        <v>-22.6066605690349</v>
       </c>
       <c r="F84">
-        <v>0.5807276852502039</v>
+        <v>0.1436858252666608</v>
       </c>
       <c r="G84">
-        <v>-1.924659631925502</v>
+        <v>-2.448285309326487</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.65169650060134</v>
       </c>
       <c r="E85">
-        <v>-21.2892731385155</v>
+        <v>-23.64229540374507</v>
       </c>
       <c r="F85">
-        <v>0.6615742885274722</v>
+        <v>0.1903267563293103</v>
       </c>
       <c r="G85">
-        <v>-2.658140791060887</v>
+        <v>-3.317293581748556</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.74243930135656</v>
       </c>
       <c r="E86">
-        <v>-22.85700819760094</v>
+        <v>-23.17250245324133</v>
       </c>
       <c r="F86">
-        <v>0.6409100937428184</v>
+        <v>-0.469536982985859</v>
       </c>
       <c r="G86">
-        <v>-0.9704114329582791</v>
+        <v>-2.169967745839958</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.83193573857435</v>
       </c>
       <c r="E87">
-        <v>-23.82294981733306</v>
+        <v>-25.48490430662209</v>
       </c>
       <c r="F87">
-        <v>0.6614396735246599</v>
+        <v>-0.2661923108552648</v>
       </c>
       <c r="G87">
-        <v>-1.475640408797534</v>
+        <v>-4.476001073221167</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.92345042538183</v>
       </c>
       <c r="E88">
-        <v>-25.2232490784589</v>
+        <v>-24.65391121231855</v>
       </c>
       <c r="F88">
-        <v>0.5531727860274729</v>
+        <v>-0.2762623049185866</v>
       </c>
       <c r="G88">
-        <v>-1.704226957193131</v>
+        <v>-4.244613803299347</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.00932903850408</v>
       </c>
       <c r="E89">
-        <v>-26.03827477341139</v>
+        <v>-26.70404196507107</v>
       </c>
       <c r="F89">
-        <v>-0.06389763574660703</v>
+        <v>0.0426105463314844</v>
       </c>
       <c r="G89">
-        <v>-1.788887538268912</v>
+        <v>-3.004271569373847</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.09199688765771</v>
       </c>
       <c r="E90">
-        <v>-25.66751049250739</v>
+        <v>-28.51836601929618</v>
       </c>
       <c r="F90">
-        <v>-0.09864414353134851</v>
+        <v>-0.670452250242169</v>
       </c>
       <c r="G90">
-        <v>-1.987169352798021</v>
+        <v>-2.008419744614603</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.16285089100686</v>
       </c>
       <c r="E91">
-        <v>-28.06390195330841</v>
+        <v>-31.47638335500249</v>
       </c>
       <c r="F91">
-        <v>-0.04060924026006996</v>
+        <v>-1.181743786512218</v>
       </c>
       <c r="G91">
-        <v>-1.370421339922878</v>
+        <v>-2.537242978512243</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.22073920475452</v>
       </c>
       <c r="E92">
-        <v>-28.90179191352563</v>
+        <v>-30.63015420990014</v>
       </c>
       <c r="F92">
-        <v>-0.60793783478907</v>
+        <v>-1.006034782606042</v>
       </c>
       <c r="G92">
-        <v>-1.651115875106603</v>
+        <v>-2.777019170830576</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.25961513820651</v>
       </c>
       <c r="E93">
-        <v>-31.18986227606318</v>
+        <v>-34.39291307608753</v>
       </c>
       <c r="F93">
-        <v>-0.5197467953289513</v>
+        <v>-1.627294106526459</v>
       </c>
       <c r="G93">
-        <v>-1.900181458208131</v>
+        <v>-3.347101733784153</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.26730919984109</v>
       </c>
       <c r="E94">
-        <v>-35.06430463246473</v>
+        <v>-34.63179460846614</v>
       </c>
       <c r="F94">
-        <v>-0.872449980491682</v>
+        <v>-0.9907171789919114</v>
       </c>
       <c r="G94">
-        <v>-2.030921522645029</v>
+        <v>-3.155613158701629</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.24123666676035</v>
       </c>
       <c r="E95">
-        <v>-34.87502574012913</v>
+        <v>-38.55356631095887</v>
       </c>
       <c r="F95">
-        <v>-1.040622127946282</v>
+        <v>-1.593437641466194</v>
       </c>
       <c r="G95">
-        <v>-3.105524604692457</v>
+        <v>-3.883271068233436</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.16678572164077</v>
       </c>
       <c r="E96">
-        <v>-38.06733726404429</v>
+        <v>-37.875289209853</v>
       </c>
       <c r="F96">
-        <v>-1.544874091422201</v>
+        <v>-1.727101628876326</v>
       </c>
       <c r="G96">
-        <v>-1.637132130748721</v>
+        <v>-4.293153021996141</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.046753873374</v>
       </c>
       <c r="E97">
-        <v>-40.18481095376488</v>
+        <v>-41.23740718787077</v>
       </c>
       <c r="F97">
-        <v>-1.820512563033733</v>
+        <v>-2.767838722325105</v>
       </c>
       <c r="G97">
-        <v>-2.458448684132049</v>
+        <v>-4.079596350348836</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.86923641627442</v>
       </c>
       <c r="E98">
-        <v>-42.00069280304864</v>
+        <v>-43.83779734576933</v>
       </c>
       <c r="F98">
-        <v>-2.191626329463447</v>
+        <v>-2.353477906609528</v>
       </c>
       <c r="G98">
-        <v>-2.873994981312447</v>
+        <v>-4.371209064721078</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.65088903579821</v>
       </c>
       <c r="E99">
-        <v>-44.07951370287675</v>
+        <v>-45.45824610654106</v>
       </c>
       <c r="F99">
-        <v>-2.211079781075748</v>
+        <v>-3.06849974740058</v>
       </c>
       <c r="G99">
-        <v>-3.253171625198412</v>
+        <v>-4.058779639997899</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.38516072132562</v>
       </c>
       <c r="E100">
-        <v>-45.90233317434026</v>
+        <v>-47.56309441072826</v>
       </c>
       <c r="F100">
-        <v>-2.817071388118372</v>
+        <v>-3.049412131854746</v>
       </c>
       <c r="G100">
-        <v>-4.008224299067688</v>
+        <v>-4.870167867308952</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.10338760768072</v>
       </c>
       <c r="E101">
-        <v>-48.52419395962768</v>
+        <v>-49.34468891906294</v>
       </c>
       <c r="F101">
-        <v>-3.105206883108636</v>
+        <v>-2.95511194682582</v>
       </c>
       <c r="G101">
-        <v>-3.913896925017234</v>
+        <v>-5.692732496360585</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.79335556706055</v>
       </c>
       <c r="E102">
-        <v>-50.4984569230927</v>
+        <v>-51.39362641891444</v>
       </c>
       <c r="F102">
-        <v>-3.242009775643169</v>
+        <v>-3.491081580523204</v>
       </c>
       <c r="G102">
-        <v>-4.910626044344386</v>
+        <v>-5.287399232168839</v>
       </c>
     </row>
   </sheetData>
